--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_3/epoch_140/per_file_predictions_epoch_140.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_3/epoch_140/per_file_predictions_epoch_140.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="526">
   <si>
     <t>Filename</t>
   </si>
@@ -826,58 +826,64 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9643,0.0023,0.0114,0.0016</t>
-  </si>
-  <si>
-    <t>0.0031,0.0061,0.0008,0.9991</t>
-  </si>
-  <si>
-    <t>0.9782,0.0024,0.0008,0.0061</t>
-  </si>
-  <si>
-    <t>0.0922,0.0015,0.0076,0.9388</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9642,0.0023,0.0114,0.0016</t>
+  </si>
+  <si>
+    <t>0.0031,0.0060,0.0008,0.9991</t>
+  </si>
+  <si>
+    <t>0.9781,0.0024,0.0008,0.0062</t>
+  </si>
+  <si>
+    <t>0.0915,0.0015,0.0076,0.9395</t>
   </si>
   <si>
     <t>0.9938,0.0015,0.0018,0.0003</t>
   </si>
   <si>
-    <t>0.9906,0.0059,0.0013,0.0004</t>
+    <t>0.9905,0.0059,0.0013,0.0004</t>
   </si>
   <si>
     <t>0.9932,0.0014,0.0020,0.0001</t>
   </si>
   <si>
-    <t>0.9917,0.0016,0.0025,0.0001</t>
+    <t>0.9916,0.0016,0.0025,0.0001</t>
   </si>
   <si>
     <t>0.9853,0.0131,0.0007,0.0006</t>
   </si>
   <si>
-    <t>0.9901,0.0058,0.0019,0.0007</t>
-  </si>
-  <si>
-    <t>0.9943,0.0010,0.0013,0.0000</t>
+    <t>0.9900,0.0058,0.0019,0.0007</t>
+  </si>
+  <si>
+    <t>0.9943,0.0010,0.0014,0.0000</t>
   </si>
   <si>
     <t>0.9943,0.0015,0.0016,0.0002</t>
   </si>
   <si>
-    <t>0.8277,0.0064,0.1594,0.0018</t>
-  </si>
-  <si>
-    <t>0.0182,0.0130,0.9755,0.0008</t>
-  </si>
-  <si>
-    <t>0.2836,0.0004,0.8543,0.0000</t>
-  </si>
-  <si>
-    <t>0.0473,0.0094,0.9523,0.0008</t>
-  </si>
-  <si>
-    <t>0.7051,0.0006,0.3705,0.0002</t>
-  </si>
-  <si>
-    <t>0.0017,0.9977,0.0150,0.0009</t>
+    <t>0.8268,0.0064,0.1605,0.0019</t>
+  </si>
+  <si>
+    <t>0.0181,0.0130,0.9755,0.0008</t>
+  </si>
+  <si>
+    <t>0.2824,0.0004,0.8550,0.0000</t>
+  </si>
+  <si>
+    <t>0.0472,0.0094,0.9524,0.0008</t>
+  </si>
+  <si>
+    <t>0.7030,0.0006,0.3732,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.9977,0.0151,0.0009</t>
   </si>
   <si>
     <t>0.0027,0.9965,0.0062,0.0014</t>
@@ -886,79 +892,79 @@
     <t>0.0311,0.9942,0.0076,0.0000</t>
   </si>
   <si>
-    <t>0.0034,0.9939,0.0089,0.0024</t>
-  </si>
-  <si>
-    <t>0.0009,0.9994,0.0129,0.0001</t>
-  </si>
-  <si>
-    <t>0.4116,0.0022,0.6854,0.0018</t>
-  </si>
-  <si>
-    <t>0.1201,0.0088,0.8994,0.0016</t>
-  </si>
-  <si>
-    <t>0.0191,0.0004,0.9914,0.0000</t>
-  </si>
-  <si>
-    <t>0.0195,0.0025,0.9855,0.0003</t>
-  </si>
-  <si>
-    <t>0.0286,0.0014,0.9836,0.0003</t>
-  </si>
-  <si>
-    <t>0.0665,0.0009,0.9629,0.0002</t>
+    <t>0.0034,0.9939,0.0090,0.0024</t>
+  </si>
+  <si>
+    <t>0.0009,0.9994,0.0130,0.0001</t>
+  </si>
+  <si>
+    <t>0.4101,0.0022,0.6867,0.0018</t>
+  </si>
+  <si>
+    <t>0.1195,0.0088,0.8999,0.0016</t>
+  </si>
+  <si>
+    <t>0.0190,0.0004,0.9914,0.0000</t>
+  </si>
+  <si>
+    <t>0.0194,0.0025,0.9855,0.0003</t>
+  </si>
+  <si>
+    <t>0.0285,0.0014,0.9837,0.0003</t>
+  </si>
+  <si>
+    <t>0.0662,0.0009,0.9630,0.0002</t>
   </si>
   <si>
     <t>0.0121,0.0009,0.9922,0.0002</t>
   </si>
   <si>
-    <t>0.7392,0.1103,0.0753,0.0017</t>
-  </si>
-  <si>
-    <t>0.7879,0.3236,0.0158,0.0028</t>
-  </si>
-  <si>
-    <t>0.0028,0.0004,0.9981,0.0003</t>
-  </si>
-  <si>
-    <t>0.0152,0.2322,0.8710,0.0015</t>
-  </si>
-  <si>
-    <t>0.8741,0.0034,0.0955,0.0009</t>
-  </si>
-  <si>
-    <t>0.6529,0.0118,0.2851,0.0013</t>
-  </si>
-  <si>
-    <t>0.3948,0.6861,0.0306,0.0011</t>
-  </si>
-  <si>
-    <t>0.0050,0.9700,0.5612,0.0015</t>
-  </si>
-  <si>
-    <t>0.0008,0.6429,0.9670,0.0004</t>
+    <t>0.7390,0.1100,0.0758,0.0017</t>
+  </si>
+  <si>
+    <t>0.7880,0.3227,0.0159,0.0028</t>
+  </si>
+  <si>
+    <t>0.0027,0.0004,0.9981,0.0003</t>
+  </si>
+  <si>
+    <t>0.0151,0.2317,0.8716,0.0015</t>
+  </si>
+  <si>
+    <t>0.8732,0.0034,0.0963,0.0009</t>
+  </si>
+  <si>
+    <t>0.6515,0.0118,0.2866,0.0013</t>
+  </si>
+  <si>
+    <t>0.3951,0.6853,0.0308,0.0011</t>
+  </si>
+  <si>
+    <t>0.0050,0.9699,0.5624,0.0015</t>
+  </si>
+  <si>
+    <t>0.0008,0.6425,0.9671,0.0004</t>
   </si>
   <si>
     <t>0.0012,0.0024,0.9978,0.0009</t>
   </si>
   <si>
-    <t>0.0094,0.0616,0.9733,0.0011</t>
-  </si>
-  <si>
-    <t>0.0999,0.0014,0.9205,0.0025</t>
-  </si>
-  <si>
-    <t>0.0006,0.6481,0.9524,0.0011</t>
-  </si>
-  <si>
-    <t>0.0012,0.9914,0.0094,0.0033</t>
-  </si>
-  <si>
-    <t>0.0024,0.0279,0.9918,0.0015</t>
-  </si>
-  <si>
-    <t>0.0003,0.8334,0.0013,0.9640</t>
+    <t>0.0093,0.0617,0.9734,0.0011</t>
+  </si>
+  <si>
+    <t>0.0992,0.0014,0.9211,0.0025</t>
+  </si>
+  <si>
+    <t>0.0006,0.6470,0.9527,0.0011</t>
+  </si>
+  <si>
+    <t>0.0012,0.9914,0.0095,0.0033</t>
+  </si>
+  <si>
+    <t>0.0024,0.0280,0.9918,0.0015</t>
+  </si>
+  <si>
+    <t>0.0003,0.8327,0.0013,0.9643</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0001,0.0001</t>
@@ -967,58 +973,58 @@
     <t>0.0002,0.9998,0.0129,0.0003</t>
   </si>
   <si>
-    <t>0.0001,0.9999,0.0063,0.0001</t>
+    <t>0.0001,0.9999,0.0064,0.0001</t>
   </si>
   <si>
     <t>0.0002,0.0069,0.9976,0.0011</t>
   </si>
   <si>
-    <t>0.0007,0.1079,0.9929,0.0012</t>
+    <t>0.0007,0.1081,0.9929,0.0012</t>
   </si>
   <si>
     <t>0.0071,0.0037,0.9912,0.0006</t>
   </si>
   <si>
-    <t>0.0207,0.0002,0.9924,0.0000</t>
+    <t>0.0206,0.0002,0.9924,0.0000</t>
   </si>
   <si>
     <t>0.0079,0.0013,0.9939,0.0001</t>
   </si>
   <si>
-    <t>0.0283,0.0145,0.9631,0.0010</t>
-  </si>
-  <si>
-    <t>0.9758,0.0065,0.0091,0.0002</t>
-  </si>
-  <si>
-    <t>0.9618,0.0003,0.0382,0.0001</t>
-  </si>
-  <si>
-    <t>0.9660,0.0135,0.0139,0.0042</t>
-  </si>
-  <si>
-    <t>0.2182,0.0010,0.8536,0.0003</t>
-  </si>
-  <si>
-    <t>0.9832,0.0002,0.0120,0.0001</t>
-  </si>
-  <si>
-    <t>0.9894,0.0014,0.0050,0.0002</t>
+    <t>0.0282,0.0145,0.9633,0.0010</t>
+  </si>
+  <si>
+    <t>0.9757,0.0065,0.0092,0.0002</t>
+  </si>
+  <si>
+    <t>0.9615,0.0003,0.0386,0.0001</t>
+  </si>
+  <si>
+    <t>0.9659,0.0135,0.0140,0.0043</t>
+  </si>
+  <si>
+    <t>0.2170,0.0010,0.8545,0.0003</t>
+  </si>
+  <si>
+    <t>0.9831,0.0002,0.0121,0.0001</t>
+  </si>
+  <si>
+    <t>0.9894,0.0014,0.0051,0.0002</t>
   </si>
   <si>
     <t>0.9932,0.0006,0.0028,0.0001</t>
   </si>
   <si>
-    <t>0.0000,0.9990,0.9155,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.1280,0.9987,0.0002</t>
+    <t>0.0000,0.9990,0.9159,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.1282,0.9987,0.0002</t>
   </si>
   <si>
     <t>0.0014,0.0131,0.9944,0.0010</t>
   </si>
   <si>
-    <t>0.0002,0.9838,0.8943,0.0004</t>
+    <t>0.0002,0.9837,0.8949,0.0004</t>
   </si>
   <si>
     <t>0.0002,0.0003,0.9996,0.0002</t>
@@ -1030,28 +1036,28 @@
     <t>0.0000,0.9999,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9802,0.0002,0.0212,0.0000</t>
-  </si>
-  <si>
-    <t>0.0955,0.0182,0.9025,0.0019</t>
-  </si>
-  <si>
-    <t>0.0112,0.0025,0.9920,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.8408,0.9846,0.0005</t>
+    <t>0.9801,0.0002,0.0214,0.0000</t>
+  </si>
+  <si>
+    <t>0.0950,0.0182,0.9029,0.0019</t>
+  </si>
+  <si>
+    <t>0.0111,0.0026,0.9920,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.8406,0.9846,0.0005</t>
   </si>
   <si>
     <t>0.0001,0.9208,0.9853,0.0002</t>
   </si>
   <si>
-    <t>0.0000,0.9997,0.3879,0.0000</t>
+    <t>0.0000,0.9997,0.3899,0.0000</t>
   </si>
   <si>
     <t>0.0001,0.9815,0.9761,0.0001</t>
   </si>
   <si>
-    <t>0.0011,0.0031,0.0012,0.9997</t>
+    <t>0.0010,0.0031,0.0012,0.9997</t>
   </si>
   <si>
     <t>0.0007,0.0007,0.0002,0.9999</t>
@@ -1063,34 +1069,34 @@
     <t>0.0017,0.0013,0.0016,0.9997</t>
   </si>
   <si>
-    <t>0.0195,0.0018,0.0039,0.9966</t>
-  </si>
-  <si>
-    <t>0.0004,0.0019,0.0027,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.9973,0.9155,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9076,0.9949,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9258,0.8687,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.4179,0.9946,0.0003</t>
+    <t>0.0194,0.0018,0.0039,0.9966</t>
+  </si>
+  <si>
+    <t>0.0004,0.0019,0.0028,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.9973,0.9159,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9075,0.9949,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9256,0.8693,0.0005</t>
+  </si>
+  <si>
+    <t>0.0003,0.4183,0.9946,0.0003</t>
   </si>
   <si>
     <t>0.0000,0.9919,0.9920,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.9903,0.7686,0.0001</t>
+    <t>0.0002,0.9903,0.7698,0.0001</t>
   </si>
   <si>
     <t>0.9945,0.0041,0.0006,0.0003</t>
   </si>
   <si>
-    <t>0.9840,0.0092,0.0033,0.0004</t>
+    <t>0.9839,0.0092,0.0033,0.0004</t>
   </si>
   <si>
     <t>0.9779,0.0267,0.0008,0.0003</t>
@@ -1111,13 +1117,13 @@
     <t>0.9976,0.0013,0.0006,0.0001</t>
   </si>
   <si>
-    <t>0.9950,0.0004,0.0013,0.0002</t>
+    <t>0.9949,0.0004,0.0014,0.0002</t>
   </si>
   <si>
     <t>0.9945,0.0026,0.0010,0.0003</t>
   </si>
   <si>
-    <t>0.9968,0.0009,0.0004,0.0001</t>
+    <t>0.9967,0.0009,0.0004,0.0001</t>
   </si>
   <si>
     <t>0.9969,0.0009,0.0005,0.0003</t>
@@ -1135,16 +1141,16 @@
     <t>0.9913,0.0012,0.0027,0.0002</t>
   </si>
   <si>
-    <t>0.0022,0.0002,0.9989,0.0000</t>
+    <t>0.0022,0.0002,0.9990,0.0000</t>
   </si>
   <si>
     <t>0.0149,0.0012,0.9899,0.0002</t>
   </si>
   <si>
-    <t>0.9653,0.0001,0.0462,0.0000</t>
-  </si>
-  <si>
-    <t>0.0262,0.0010,0.9839,0.0001</t>
+    <t>0.9651,0.0001,0.0465,0.0000</t>
+  </si>
+  <si>
+    <t>0.0262,0.0010,0.9840,0.0001</t>
   </si>
   <si>
     <t>0.0002,0.9997,0.0004,0.0001</t>
@@ -1153,10 +1159,10 @@
     <t>0.0001,0.9999,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.2529,0.8625,0.0037,0.0005</t>
-  </si>
-  <si>
-    <t>0.0424,0.9686,0.0173,0.0026</t>
+    <t>0.2525,0.8624,0.0037,0.0005</t>
+  </si>
+  <si>
+    <t>0.0425,0.9685,0.0174,0.0027</t>
   </si>
   <si>
     <t>0.0005,0.9994,0.0006,0.0001</t>
@@ -1165,22 +1171,22 @@
     <t>0.0001,0.9999,0.0004,0.0001</t>
   </si>
   <si>
-    <t>0.6617,0.4275,0.0223,0.0007</t>
-  </si>
-  <si>
-    <t>0.0861,0.0159,0.9147,0.0030</t>
-  </si>
-  <si>
-    <t>0.0277,0.0071,0.9724,0.0007</t>
-  </si>
-  <si>
-    <t>0.3177,0.0113,0.6888,0.0023</t>
-  </si>
-  <si>
-    <t>0.1085,0.0140,0.9046,0.0029</t>
-  </si>
-  <si>
-    <t>0.0002,0.5927,0.4945,0.2482</t>
+    <t>0.6615,0.4272,0.0225,0.0007</t>
+  </si>
+  <si>
+    <t>0.0857,0.0159,0.9152,0.0030</t>
+  </si>
+  <si>
+    <t>0.0277,0.0072,0.9724,0.0007</t>
+  </si>
+  <si>
+    <t>0.3160,0.0112,0.6907,0.0023</t>
+  </si>
+  <si>
+    <t>0.1078,0.0139,0.9053,0.0029</t>
+  </si>
+  <si>
+    <t>0.0002,0.5919,0.4955,0.2481</t>
   </si>
   <si>
     <t>0.0002,0.9998,0.0011,0.0001</t>
@@ -1192,64 +1198,64 @@
     <t>0.0002,0.9988,0.0010,0.0074</t>
   </si>
   <si>
-    <t>0.0003,0.9992,0.0648,0.0012</t>
-  </si>
-  <si>
-    <t>0.0031,0.9952,0.0597,0.0004</t>
-  </si>
-  <si>
-    <t>0.4420,0.5306,0.0809,0.0026</t>
-  </si>
-  <si>
-    <t>0.2138,0.7958,0.0326,0.0061</t>
+    <t>0.0003,0.9992,0.0651,0.0012</t>
+  </si>
+  <si>
+    <t>0.0031,0.9952,0.0600,0.0004</t>
+  </si>
+  <si>
+    <t>0.4416,0.5304,0.0813,0.0027</t>
+  </si>
+  <si>
+    <t>0.2138,0.7955,0.0328,0.0062</t>
   </si>
   <si>
     <t>0.9966,0.0003,0.0007,0.0003</t>
   </si>
   <si>
-    <t>0.9802,0.0106,0.0017,0.0025</t>
-  </si>
-  <si>
-    <t>0.9888,0.0032,0.0019,0.0009</t>
-  </si>
-  <si>
-    <t>0.9858,0.0014,0.0067,0.0004</t>
+    <t>0.9801,0.0106,0.0017,0.0026</t>
+  </si>
+  <si>
+    <t>0.9888,0.0032,0.0020,0.0009</t>
+  </si>
+  <si>
+    <t>0.9858,0.0014,0.0068,0.0004</t>
   </si>
   <si>
     <t>0.9984,0.0002,0.0002,0.0001</t>
   </si>
   <si>
-    <t>0.9837,0.0018,0.0058,0.0010</t>
+    <t>0.9836,0.0018,0.0058,0.0011</t>
   </si>
   <si>
     <t>0.9874,0.0017,0.0036,0.0004</t>
   </si>
   <si>
-    <t>0.9870,0.0006,0.0057,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.9620,0.9677,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.3391,0.9959,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0175,0.9985,0.0003</t>
-  </si>
-  <si>
-    <t>0.0039,0.0051,0.9956,0.0001</t>
-  </si>
-  <si>
-    <t>0.9386,0.0014,0.0503,0.0004</t>
-  </si>
-  <si>
-    <t>0.4251,0.3300,0.0925,0.0050</t>
-  </si>
-  <si>
-    <t>0.1555,0.0004,0.9168,0.0004</t>
-  </si>
-  <si>
-    <t>0.7982,0.0031,0.2104,0.0013</t>
+    <t>0.9869,0.0006,0.0058,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.9619,0.9679,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.3392,0.9959,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0176,0.9985,0.0003</t>
+  </si>
+  <si>
+    <t>0.0039,0.0052,0.9956,0.0001</t>
+  </si>
+  <si>
+    <t>0.9382,0.0014,0.0508,0.0004</t>
+  </si>
+  <si>
+    <t>0.4247,0.3294,0.0933,0.0050</t>
+  </si>
+  <si>
+    <t>0.1553,0.0004,0.9169,0.0004</t>
+  </si>
+  <si>
+    <t>0.7974,0.0031,0.2115,0.0013</t>
   </si>
   <si>
     <t>0.0037,0.0005,0.0029,0.9993</t>
@@ -1264,55 +1270,55 @@
     <t>0.0042,0.0003,0.0021,0.9994</t>
   </si>
   <si>
-    <t>0.0001,0.9890,0.9742,0.0001</t>
-  </si>
-  <si>
-    <t>0.9680,0.0006,0.0211,0.0004</t>
-  </si>
-  <si>
-    <t>0.0117,0.9830,0.0225,0.0085</t>
+    <t>0.0001,0.9890,0.9743,0.0001</t>
+  </si>
+  <si>
+    <t>0.9677,0.0006,0.0214,0.0004</t>
+  </si>
+  <si>
+    <t>0.0117,0.9830,0.0226,0.0086</t>
   </si>
   <si>
     <t>0.9925,0.0004,0.0033,0.0001</t>
   </si>
   <si>
-    <t>0.0170,0.9818,0.0196,0.0016</t>
-  </si>
-  <si>
-    <t>0.9908,0.0011,0.0017,0.0010</t>
-  </si>
-  <si>
-    <t>0.7878,0.0000,0.4939,0.0000</t>
-  </si>
-  <si>
-    <t>0.6550,0.0000,0.5997,0.0000</t>
+    <t>0.0170,0.9817,0.0197,0.0016</t>
+  </si>
+  <si>
+    <t>0.9908,0.0011,0.0017,0.0011</t>
+  </si>
+  <si>
+    <t>0.7871,0.0000,0.4952,0.0000</t>
+  </si>
+  <si>
+    <t>0.6540,0.0000,0.6008,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.8934,0.0003,0.0771,0.0004</t>
-  </si>
-  <si>
-    <t>0.9610,0.0177,0.0126,0.0010</t>
-  </si>
-  <si>
-    <t>0.5557,0.2281,0.0646,0.0032</t>
+    <t>0.8927,0.0003,0.0776,0.0004</t>
+  </si>
+  <si>
+    <t>0.9608,0.0178,0.0127,0.0010</t>
+  </si>
+  <si>
+    <t>0.5554,0.2281,0.0648,0.0032</t>
   </si>
   <si>
     <t>0.9873,0.0008,0.0061,0.0001</t>
   </si>
   <si>
-    <t>0.9271,0.0192,0.0248,0.0012</t>
-  </si>
-  <si>
-    <t>0.2278,0.6742,0.0882,0.0214</t>
-  </si>
-  <si>
-    <t>0.8933,0.0166,0.0516,0.0008</t>
-  </si>
-  <si>
-    <t>0.9412,0.0012,0.0518,0.0003</t>
+    <t>0.9269,0.0192,0.0250,0.0012</t>
+  </si>
+  <si>
+    <t>0.2279,0.6737,0.0886,0.0216</t>
+  </si>
+  <si>
+    <t>0.8928,0.0166,0.0520,0.0009</t>
+  </si>
+  <si>
+    <t>0.9408,0.0012,0.0523,0.0003</t>
   </si>
   <si>
     <t>0.9929,0.0024,0.0017,0.0002</t>
@@ -1324,13 +1330,13 @@
     <t>0.9896,0.0014,0.0035,0.0003</t>
   </si>
   <si>
-    <t>0.9814,0.0008,0.0087,0.0002</t>
+    <t>0.9813,0.0008,0.0088,0.0002</t>
   </si>
   <si>
     <t>0.9928,0.0022,0.0016,0.0002</t>
   </si>
   <si>
-    <t>0.9890,0.0037,0.0024,0.0004</t>
+    <t>0.9890,0.0038,0.0025,0.0004</t>
   </si>
   <si>
     <t>0.9912,0.0025,0.0019,0.0002</t>
@@ -1339,46 +1345,46 @@
     <t>0.9884,0.0012,0.0034,0.0001</t>
   </si>
   <si>
-    <t>0.6780,0.3652,0.0037,0.0023</t>
-  </si>
-  <si>
-    <t>0.2684,0.7205,0.0349,0.0167</t>
-  </si>
-  <si>
-    <t>0.8537,0.1146,0.0095,0.0012</t>
-  </si>
-  <si>
-    <t>0.8965,0.0320,0.0452,0.0021</t>
-  </si>
-  <si>
-    <t>0.9823,0.0061,0.0052,0.0002</t>
-  </si>
-  <si>
-    <t>0.9526,0.0303,0.0094,0.0009</t>
-  </si>
-  <si>
-    <t>0.9826,0.0015,0.0095,0.0002</t>
-  </si>
-  <si>
-    <t>0.9320,0.0235,0.0246,0.0016</t>
+    <t>0.6778,0.3647,0.0037,0.0023</t>
+  </si>
+  <si>
+    <t>0.2683,0.7203,0.0351,0.0169</t>
+  </si>
+  <si>
+    <t>0.8533,0.1148,0.0095,0.0012</t>
+  </si>
+  <si>
+    <t>0.8953,0.0322,0.0458,0.0021</t>
+  </si>
+  <si>
+    <t>0.9822,0.0061,0.0052,0.0002</t>
+  </si>
+  <si>
+    <t>0.9524,0.0304,0.0095,0.0009</t>
+  </si>
+  <si>
+    <t>0.9825,0.0015,0.0096,0.0002</t>
+  </si>
+  <si>
+    <t>0.9317,0.0235,0.0248,0.0016</t>
   </si>
   <si>
     <t>0.0088,0.0022,0.9945,0.0001</t>
   </si>
   <si>
-    <t>0.9288,0.0367,0.0146,0.0004</t>
+    <t>0.9286,0.0369,0.0147,0.0004</t>
   </si>
   <si>
     <t>0.0004,0.0005,0.9996,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.0447,0.9931,0.0044</t>
-  </si>
-  <si>
-    <t>0.0114,0.0018,0.9913,0.0005</t>
-  </si>
-  <si>
-    <t>0.0022,0.2551,0.9786,0.0007</t>
+    <t>0.0002,0.0448,0.9931,0.0044</t>
+  </si>
+  <si>
+    <t>0.0113,0.0018,0.9913,0.0005</t>
+  </si>
+  <si>
+    <t>0.0022,0.2547,0.9787,0.0007</t>
   </si>
   <si>
     <t>0.0015,0.0026,0.9981,0.0001</t>
@@ -1390,67 +1396,67 @@
     <t>0.0120,0.0013,0.9919,0.0001</t>
   </si>
   <si>
-    <t>0.1029,0.0046,0.9219,0.0006</t>
-  </si>
-  <si>
-    <t>0.1301,0.0018,0.9172,0.0003</t>
-  </si>
-  <si>
-    <t>0.7552,0.0353,0.1597,0.0024</t>
-  </si>
-  <si>
-    <t>0.0656,0.0232,0.9049,0.0014</t>
-  </si>
-  <si>
-    <t>0.0160,0.0437,0.9525,0.0003</t>
-  </si>
-  <si>
-    <t>0.0783,0.0035,0.9409,0.0007</t>
-  </si>
-  <si>
-    <t>0.2297,0.0060,0.8104,0.0028</t>
-  </si>
-  <si>
-    <t>0.6198,0.0348,0.2858,0.0013</t>
-  </si>
-  <si>
-    <t>0.1187,0.9484,0.0100,0.0003</t>
+    <t>0.1023,0.0046,0.9223,0.0006</t>
+  </si>
+  <si>
+    <t>0.1296,0.0018,0.9175,0.0003</t>
+  </si>
+  <si>
+    <t>0.7546,0.0353,0.1604,0.0024</t>
+  </si>
+  <si>
+    <t>0.0653,0.0231,0.9054,0.0014</t>
+  </si>
+  <si>
+    <t>0.0159,0.0435,0.9528,0.0003</t>
+  </si>
+  <si>
+    <t>0.0781,0.0035,0.9411,0.0007</t>
+  </si>
+  <si>
+    <t>0.2285,0.0060,0.8116,0.0028</t>
+  </si>
+  <si>
+    <t>0.6187,0.0348,0.2872,0.0014</t>
+  </si>
+  <si>
+    <t>0.1185,0.9483,0.0101,0.0003</t>
   </si>
   <si>
     <t>0.0026,0.9973,0.0065,0.0007</t>
   </si>
   <si>
-    <t>0.0574,0.9537,0.0064,0.0022</t>
-  </si>
-  <si>
-    <t>0.9724,0.0090,0.0081,0.0002</t>
-  </si>
-  <si>
-    <t>0.3830,0.6736,0.0109,0.0008</t>
-  </si>
-  <si>
-    <t>0.3450,0.5370,0.0285,0.0005</t>
-  </si>
-  <si>
-    <t>0.9527,0.0058,0.0186,0.0002</t>
-  </si>
-  <si>
-    <t>0.3461,0.0369,0.6149,0.0110</t>
-  </si>
-  <si>
-    <t>0.1332,0.0035,0.8948,0.0027</t>
-  </si>
-  <si>
-    <t>0.4987,0.0118,0.4628,0.0030</t>
+    <t>0.0573,0.9536,0.0064,0.0022</t>
+  </si>
+  <si>
+    <t>0.9723,0.0090,0.0081,0.0002</t>
+  </si>
+  <si>
+    <t>0.3822,0.6739,0.0110,0.0008</t>
+  </si>
+  <si>
+    <t>0.3451,0.5361,0.0287,0.0006</t>
+  </si>
+  <si>
+    <t>0.9525,0.0058,0.0188,0.0002</t>
+  </si>
+  <si>
+    <t>0.3442,0.0369,0.6171,0.0110</t>
+  </si>
+  <si>
+    <t>0.1326,0.0035,0.8952,0.0027</t>
+  </si>
+  <si>
+    <t>0.4967,0.0118,0.4655,0.0030</t>
   </si>
   <si>
     <t>0.0102,0.0017,0.9918,0.0003</t>
   </si>
   <si>
-    <t>0.0956,0.0031,0.9111,0.0003</t>
-  </si>
-  <si>
-    <t>0.0319,0.0284,0.9366,0.0002</t>
+    <t>0.0950,0.0031,0.9117,0.0003</t>
+  </si>
+  <si>
+    <t>0.0317,0.0283,0.9370,0.0002</t>
   </si>
   <si>
     <t>0.0025,0.0091,0.9952,0.0006</t>
@@ -1462,34 +1468,34 @@
     <t>0.9936,0.0004,0.0019,0.0001</t>
   </si>
   <si>
-    <t>0.9790,0.0093,0.0056,0.0007</t>
-  </si>
-  <si>
-    <t>0.9764,0.0092,0.0044,0.0033</t>
-  </si>
-  <si>
-    <t>0.9893,0.0070,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9602,0.0245,0.0090,0.0026</t>
-  </si>
-  <si>
-    <t>0.9691,0.0213,0.0059,0.0017</t>
+    <t>0.9789,0.0093,0.0057,0.0007</t>
+  </si>
+  <si>
+    <t>0.9763,0.0092,0.0044,0.0033</t>
+  </si>
+  <si>
+    <t>0.9892,0.0070,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9602,0.0244,0.0091,0.0026</t>
+  </si>
+  <si>
+    <t>0.9690,0.0213,0.0059,0.0017</t>
   </si>
   <si>
     <t>0.9903,0.0059,0.0017,0.0006</t>
   </si>
   <si>
-    <t>0.9925,0.0009,0.0023,0.0001</t>
+    <t>0.9924,0.0009,0.0023,0.0001</t>
   </si>
   <si>
     <t>0.0073,0.0026,0.9942,0.0004</t>
   </si>
   <si>
-    <t>0.0531,0.0157,0.9344,0.0008</t>
-  </si>
-  <si>
-    <t>0.3937,0.0051,0.6233,0.0118</t>
+    <t>0.0526,0.0156,0.9349,0.0008</t>
+  </si>
+  <si>
+    <t>0.3918,0.0052,0.6252,0.0118</t>
   </si>
   <si>
     <t>0.0018,0.0006,0.9988,0.0001</t>
@@ -1498,55 +1504,55 @@
     <t>0.0003,0.0017,0.9994,0.0001</t>
   </si>
   <si>
-    <t>0.0055,0.0170,0.9893,0.0005</t>
+    <t>0.0055,0.0169,0.9893,0.0005</t>
   </si>
   <si>
     <t>0.0002,0.0000,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0127,0.0078,0.9846,0.0002</t>
+    <t>0.0127,0.0078,0.9847,0.0002</t>
   </si>
   <si>
     <t>0.0038,0.0064,0.9947,0.0003</t>
   </si>
   <si>
-    <t>0.0513,0.0118,0.9427,0.0019</t>
-  </si>
-  <si>
-    <t>0.7792,0.0015,0.2607,0.0008</t>
-  </si>
-  <si>
-    <t>0.4812,0.0012,0.5587,0.0045</t>
-  </si>
-  <si>
-    <t>0.9435,0.0074,0.0271,0.0002</t>
-  </si>
-  <si>
-    <t>0.9941,0.0015,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.9884,0.0105,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.9933,0.0027,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9488,0.0315,0.0078,0.0011</t>
-  </si>
-  <si>
-    <t>0.9923,0.0010,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.9869,0.0084,0.0024,0.0004</t>
+    <t>0.0511,0.0118,0.9430,0.0019</t>
+  </si>
+  <si>
+    <t>0.7779,0.0015,0.2627,0.0008</t>
+  </si>
+  <si>
+    <t>0.4795,0.0012,0.5604,0.0045</t>
+  </si>
+  <si>
+    <t>0.9432,0.0074,0.0273,0.0002</t>
+  </si>
+  <si>
+    <t>0.9941,0.0015,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9883,0.0105,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9933,0.0027,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.9487,0.0316,0.0079,0.0011</t>
+  </si>
+  <si>
+    <t>0.9922,0.0010,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.9868,0.0085,0.0024,0.0004</t>
   </si>
   <si>
     <t>0.9948,0.0017,0.0009,0.0002</t>
   </si>
   <si>
-    <t>0.9850,0.0018,0.0049,0.0013</t>
-  </si>
-  <si>
-    <t>0.0091,0.0210,0.9830,0.0004</t>
+    <t>0.9849,0.0018,0.0049,0.0013</t>
+  </si>
+  <si>
+    <t>0.0091,0.0210,0.9831,0.0004</t>
   </si>
   <si>
     <t>0.0009,0.0028,0.9989,0.0000</t>
@@ -1555,22 +1561,22 @@
     <t>0.0021,0.0019,0.9980,0.0000</t>
   </si>
   <si>
-    <t>0.0133,0.0337,0.9663,0.0005</t>
+    <t>0.0133,0.0335,0.9666,0.0005</t>
   </si>
   <si>
     <t>0.0105,0.0016,0.9924,0.0001</t>
   </si>
   <si>
-    <t>0.6685,0.0408,0.1860,0.0054</t>
-  </si>
-  <si>
-    <t>0.0575,0.0177,0.9264,0.0039</t>
+    <t>0.6677,0.0407,0.1868,0.0054</t>
+  </si>
+  <si>
+    <t>0.0572,0.0177,0.9267,0.0039</t>
   </si>
   <si>
     <t>0.0015,0.0005,0.9982,0.0008</t>
   </si>
   <si>
-    <t>0.9619,0.0007,0.0067,0.0043</t>
+    <t>0.9616,0.0007,0.0067,0.0044</t>
   </si>
   <si>
     <t>0.0007,0.0033,0.0002,0.9998</t>
@@ -1585,7 +1591,7 @@
     <t>0.0002,0.0002,0.0013,0.9999</t>
   </si>
   <si>
-    <t>0.7170,0.0124,0.0213,0.1695</t>
+    <t>0.7156,0.0124,0.0214,0.1710</t>
   </si>
 </sst>
 </file>
@@ -1971,7 +1977,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1985,7 +1991,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1999,7 +2005,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2013,7 +2019,7 @@
         <v>265</v>
       </c>
       <c r="D5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2027,7 +2033,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2041,7 +2047,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2055,7 +2061,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2069,7 +2075,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2083,7 +2089,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2097,7 +2103,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2111,7 +2117,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2125,7 +2131,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2139,7 +2145,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2153,7 +2159,7 @@
         <v>266</v>
       </c>
       <c r="D15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2167,7 +2173,7 @@
         <v>266</v>
       </c>
       <c r="D16" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2181,7 +2187,7 @@
         <v>266</v>
       </c>
       <c r="D17" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2195,7 +2201,7 @@
         <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2209,7 +2215,7 @@
         <v>267</v>
       </c>
       <c r="D19" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2223,7 +2229,7 @@
         <v>267</v>
       </c>
       <c r="D20" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2237,7 +2243,7 @@
         <v>267</v>
       </c>
       <c r="D21" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2251,7 +2257,7 @@
         <v>267</v>
       </c>
       <c r="D22" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2265,7 +2271,7 @@
         <v>267</v>
       </c>
       <c r="D23" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2279,7 +2285,7 @@
         <v>266</v>
       </c>
       <c r="D24" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2293,7 +2299,7 @@
         <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2307,7 +2313,7 @@
         <v>266</v>
       </c>
       <c r="D26" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2321,7 +2327,7 @@
         <v>266</v>
       </c>
       <c r="D27" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2335,7 +2341,7 @@
         <v>266</v>
       </c>
       <c r="D28" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2349,7 +2355,7 @@
         <v>266</v>
       </c>
       <c r="D29" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2363,7 +2369,7 @@
         <v>266</v>
       </c>
       <c r="D30" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2377,7 +2383,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2391,7 +2397,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2405,7 +2411,7 @@
         <v>266</v>
       </c>
       <c r="D33" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2419,7 +2425,7 @@
         <v>266</v>
       </c>
       <c r="D34" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2433,7 +2439,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2447,7 +2453,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2461,7 +2467,7 @@
         <v>267</v>
       </c>
       <c r="D37" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2475,7 +2481,7 @@
         <v>268</v>
       </c>
       <c r="D38" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2489,7 +2495,7 @@
         <v>268</v>
       </c>
       <c r="D39" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2503,7 +2509,7 @@
         <v>266</v>
       </c>
       <c r="D40" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2517,7 +2523,7 @@
         <v>266</v>
       </c>
       <c r="D41" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2531,7 +2537,7 @@
         <v>266</v>
       </c>
       <c r="D42" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2545,7 +2551,7 @@
         <v>268</v>
       </c>
       <c r="D43" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2559,7 +2565,7 @@
         <v>267</v>
       </c>
       <c r="D44" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2573,7 +2579,7 @@
         <v>266</v>
       </c>
       <c r="D45" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2587,7 +2593,7 @@
         <v>269</v>
       </c>
       <c r="D46" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2601,7 +2607,7 @@
         <v>267</v>
       </c>
       <c r="D47" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2615,7 +2621,7 @@
         <v>267</v>
       </c>
       <c r="D48" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2629,7 +2635,7 @@
         <v>267</v>
       </c>
       <c r="D49" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2643,7 +2649,7 @@
         <v>266</v>
       </c>
       <c r="D50" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2657,7 +2663,7 @@
         <v>266</v>
       </c>
       <c r="D51" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2671,7 +2677,7 @@
         <v>266</v>
       </c>
       <c r="D52" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2685,7 +2691,7 @@
         <v>266</v>
       </c>
       <c r="D53" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2699,7 +2705,7 @@
         <v>266</v>
       </c>
       <c r="D54" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2713,7 +2719,7 @@
         <v>266</v>
       </c>
       <c r="D55" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2727,7 +2733,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2741,7 +2747,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2755,7 +2761,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2769,7 +2775,7 @@
         <v>266</v>
       </c>
       <c r="D59" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2783,7 +2789,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2797,7 +2803,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2811,7 +2817,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2825,7 +2831,7 @@
         <v>268</v>
       </c>
       <c r="D63" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2839,7 +2845,7 @@
         <v>266</v>
       </c>
       <c r="D64" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2853,7 +2859,7 @@
         <v>266</v>
       </c>
       <c r="D65" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2867,7 +2873,7 @@
         <v>268</v>
       </c>
       <c r="D66" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2881,7 +2887,7 @@
         <v>266</v>
       </c>
       <c r="D67" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2895,7 +2901,7 @@
         <v>267</v>
       </c>
       <c r="D68" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2909,7 +2915,7 @@
         <v>267</v>
       </c>
       <c r="D69" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2923,7 +2929,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2937,7 +2943,7 @@
         <v>266</v>
       </c>
       <c r="D71" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2951,7 +2957,7 @@
         <v>266</v>
       </c>
       <c r="D72" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2965,7 +2971,7 @@
         <v>268</v>
       </c>
       <c r="D73" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2979,7 +2985,7 @@
         <v>268</v>
       </c>
       <c r="D74" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2993,7 +2999,7 @@
         <v>267</v>
       </c>
       <c r="D75" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3007,7 +3013,7 @@
         <v>268</v>
       </c>
       <c r="D76" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3021,7 +3027,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3035,7 +3041,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3049,7 +3055,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3063,7 +3069,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3077,7 +3083,7 @@
         <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3091,7 +3097,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3105,7 +3111,7 @@
         <v>268</v>
       </c>
       <c r="D83" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3119,7 +3125,7 @@
         <v>268</v>
       </c>
       <c r="D84" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3133,7 +3139,7 @@
         <v>268</v>
       </c>
       <c r="D85" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3147,7 +3153,7 @@
         <v>266</v>
       </c>
       <c r="D86" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3161,7 +3167,7 @@
         <v>268</v>
       </c>
       <c r="D87" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3175,7 +3181,7 @@
         <v>268</v>
       </c>
       <c r="D88" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3189,7 +3195,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3203,7 +3209,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3217,7 +3223,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3231,7 +3237,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3245,7 +3251,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3259,7 +3265,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3273,7 +3279,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3287,7 +3293,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3301,7 +3307,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3315,7 +3321,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3329,7 +3335,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3343,7 +3349,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3357,7 +3363,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3371,7 +3377,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3385,7 +3391,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3399,7 +3405,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3413,7 +3419,7 @@
         <v>266</v>
       </c>
       <c r="D105" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3427,7 +3433,7 @@
         <v>266</v>
       </c>
       <c r="D106" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3441,7 +3447,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3455,7 +3461,7 @@
         <v>266</v>
       </c>
       <c r="D108" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3469,7 +3475,7 @@
         <v>267</v>
       </c>
       <c r="D109" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3483,7 +3489,7 @@
         <v>267</v>
       </c>
       <c r="D110" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3497,7 +3503,7 @@
         <v>267</v>
       </c>
       <c r="D111" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3511,7 +3517,7 @@
         <v>267</v>
       </c>
       <c r="D112" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3525,7 +3531,7 @@
         <v>267</v>
       </c>
       <c r="D113" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3539,7 +3545,7 @@
         <v>267</v>
       </c>
       <c r="D114" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3553,7 +3559,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3567,7 +3573,7 @@
         <v>266</v>
       </c>
       <c r="D116" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3581,7 +3587,7 @@
         <v>266</v>
       </c>
       <c r="D117" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3595,7 +3601,7 @@
         <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3609,7 +3615,7 @@
         <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3623,7 +3629,7 @@
         <v>267</v>
       </c>
       <c r="D120" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3637,7 +3643,7 @@
         <v>267</v>
       </c>
       <c r="D121" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3651,7 +3657,7 @@
         <v>267</v>
       </c>
       <c r="D122" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3665,7 +3671,7 @@
         <v>267</v>
       </c>
       <c r="D123" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3679,7 +3685,7 @@
         <v>267</v>
       </c>
       <c r="D124" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3693,7 +3699,7 @@
         <v>267</v>
       </c>
       <c r="D125" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3707,7 +3713,7 @@
         <v>267</v>
       </c>
       <c r="D126" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3721,7 +3727,7 @@
         <v>267</v>
       </c>
       <c r="D127" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3735,7 +3741,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3749,7 +3755,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3763,7 +3769,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3777,7 +3783,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3791,7 +3797,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3805,7 +3811,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3819,7 +3825,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3833,7 +3839,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3847,7 +3853,7 @@
         <v>268</v>
       </c>
       <c r="D136" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3861,7 +3867,7 @@
         <v>266</v>
       </c>
       <c r="D137" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3875,7 +3881,7 @@
         <v>266</v>
       </c>
       <c r="D138" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3889,7 +3895,7 @@
         <v>266</v>
       </c>
       <c r="D139" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3903,7 +3909,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3914,10 +3920,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D141" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3931,7 +3937,7 @@
         <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3945,7 +3951,7 @@
         <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3959,7 +3965,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3973,7 +3979,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3987,7 +3993,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4001,7 +4007,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4015,7 +4021,7 @@
         <v>268</v>
       </c>
       <c r="D148" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4029,7 +4035,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4043,7 +4049,7 @@
         <v>267</v>
       </c>
       <c r="D150" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4057,7 +4063,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4071,7 +4077,7 @@
         <v>267</v>
       </c>
       <c r="D152" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4085,7 +4091,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4099,7 +4105,7 @@
         <v>264</v>
       </c>
       <c r="D154" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4110,10 +4116,10 @@
         <v>259</v>
       </c>
       <c r="C155" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D155" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4127,7 +4133,7 @@
         <v>266</v>
       </c>
       <c r="D156" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4141,7 +4147,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4155,7 +4161,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4169,7 +4175,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4183,7 +4189,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4197,7 +4203,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4211,7 +4217,7 @@
         <v>267</v>
       </c>
       <c r="D162" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4225,7 +4231,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4239,7 +4245,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4253,7 +4259,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4267,7 +4273,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4281,7 +4287,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4295,7 +4301,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4309,7 +4315,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4323,7 +4329,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4337,7 +4343,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4351,7 +4357,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4365,7 +4371,7 @@
         <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4379,7 +4385,7 @@
         <v>267</v>
       </c>
       <c r="D174" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4393,7 +4399,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4407,7 +4413,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4421,7 +4427,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4435,7 +4441,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4449,7 +4455,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4463,7 +4469,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4477,7 +4483,7 @@
         <v>266</v>
       </c>
       <c r="D181" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4491,7 +4497,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4505,7 +4511,7 @@
         <v>266</v>
       </c>
       <c r="D183" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4519,7 +4525,7 @@
         <v>266</v>
       </c>
       <c r="D184" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4533,7 +4539,7 @@
         <v>266</v>
       </c>
       <c r="D185" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4547,7 +4553,7 @@
         <v>266</v>
       </c>
       <c r="D186" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4561,7 +4567,7 @@
         <v>266</v>
       </c>
       <c r="D187" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4575,7 +4581,7 @@
         <v>266</v>
       </c>
       <c r="D188" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4589,7 +4595,7 @@
         <v>266</v>
       </c>
       <c r="D189" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4603,7 +4609,7 @@
         <v>266</v>
       </c>
       <c r="D190" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4617,7 +4623,7 @@
         <v>266</v>
       </c>
       <c r="D191" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4631,7 +4637,7 @@
         <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4645,7 +4651,7 @@
         <v>266</v>
       </c>
       <c r="D193" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4659,7 +4665,7 @@
         <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4673,7 +4679,7 @@
         <v>266</v>
       </c>
       <c r="D195" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4687,7 +4693,7 @@
         <v>266</v>
       </c>
       <c r="D196" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4701,7 +4707,7 @@
         <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4715,7 +4721,7 @@
         <v>267</v>
       </c>
       <c r="D198" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4729,7 +4735,7 @@
         <v>267</v>
       </c>
       <c r="D199" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4743,7 +4749,7 @@
         <v>267</v>
       </c>
       <c r="D200" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4757,7 +4763,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4771,7 +4777,7 @@
         <v>267</v>
       </c>
       <c r="D202" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4785,7 +4791,7 @@
         <v>267</v>
       </c>
       <c r="D203" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4799,7 +4805,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4813,7 +4819,7 @@
         <v>266</v>
       </c>
       <c r="D205" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4827,7 +4833,7 @@
         <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4838,10 +4844,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D207" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4855,7 +4861,7 @@
         <v>266</v>
       </c>
       <c r="D208" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4869,7 +4875,7 @@
         <v>266</v>
       </c>
       <c r="D209" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4883,7 +4889,7 @@
         <v>266</v>
       </c>
       <c r="D210" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4897,7 +4903,7 @@
         <v>266</v>
       </c>
       <c r="D211" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4911,7 +4917,7 @@
         <v>266</v>
       </c>
       <c r="D212" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4925,7 +4931,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4939,7 +4945,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4953,7 +4959,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4967,7 +4973,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4981,7 +4987,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4995,7 +5001,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5009,7 +5015,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5023,7 +5029,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5037,7 +5043,7 @@
         <v>266</v>
       </c>
       <c r="D221" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5051,7 +5057,7 @@
         <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5065,7 +5071,7 @@
         <v>266</v>
       </c>
       <c r="D223" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5079,7 +5085,7 @@
         <v>266</v>
       </c>
       <c r="D224" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5093,7 +5099,7 @@
         <v>266</v>
       </c>
       <c r="D225" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5107,7 +5113,7 @@
         <v>266</v>
       </c>
       <c r="D226" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5121,7 +5127,7 @@
         <v>266</v>
       </c>
       <c r="D227" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5135,7 +5141,7 @@
         <v>266</v>
       </c>
       <c r="D228" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5149,7 +5155,7 @@
         <v>266</v>
       </c>
       <c r="D229" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5163,7 +5169,7 @@
         <v>266</v>
       </c>
       <c r="D230" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5177,7 +5183,7 @@
         <v>266</v>
       </c>
       <c r="D231" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5191,7 +5197,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5205,7 +5211,7 @@
         <v>266</v>
       </c>
       <c r="D233" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5219,7 +5225,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5233,7 +5239,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5247,7 +5253,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5261,7 +5267,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5275,7 +5281,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5289,7 +5295,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5303,7 +5309,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5317,7 +5323,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5331,7 +5337,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5345,7 +5351,7 @@
         <v>266</v>
       </c>
       <c r="D243" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5359,7 +5365,7 @@
         <v>266</v>
       </c>
       <c r="D244" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5373,7 +5379,7 @@
         <v>266</v>
       </c>
       <c r="D245" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5387,7 +5393,7 @@
         <v>266</v>
       </c>
       <c r="D246" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5401,7 +5407,7 @@
         <v>266</v>
       </c>
       <c r="D247" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5415,7 +5421,7 @@
         <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5429,7 +5435,7 @@
         <v>266</v>
       </c>
       <c r="D249" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5443,7 +5449,7 @@
         <v>266</v>
       </c>
       <c r="D250" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5457,7 +5463,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5471,7 +5477,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5485,7 +5491,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5499,7 +5505,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5513,7 +5519,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5527,7 +5533,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
